--- a/public/exports-60-250/29189641.xlsx
+++ b/public/exports-60-250/29189641.xlsx
@@ -3589,7 +3589,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">200012236</t>
+          <t xml:space="preserve">200012231</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311478273</t>
+          <t xml:space="preserve">311437743</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
